--- a/samples/프레스로그_샘플_2026-08.xlsx
+++ b/samples/프레스로그_샘플_2026-08.xlsx
@@ -436,7 +436,7 @@
         <v>프레스 누적 타수</v>
       </c>
       <c r="F2" t="str">
-        <v>금형 타수</v>
+        <v>타수</v>
       </c>
       <c r="G2" t="str">
         <v>가동 시간(h)</v>
